--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -794,6 +794,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 2025</t>
   </si>
   <si>
     <t xml:space="preserve">inflation</t>
@@ -3295,7 +3298,7 @@
         <v>257</v>
       </c>
       <c r="B257" t="n">
-        <v>2.17723026042671</v>
+        <v>2.08398976978965</v>
       </c>
     </row>
     <row r="258">
@@ -3303,7 +3306,7 @@
         <v>258</v>
       </c>
       <c r="B258" t="n">
-        <v>-1.84940645557947</v>
+        <v>-0.937137943003352</v>
       </c>
     </row>
     <row r="259">
@@ -3311,7 +3314,15 @@
         <v>259</v>
       </c>
       <c r="B259" t="n">
-        <v>2.60343030028252</v>
+        <v>2.38566269456462</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.604381240998075</v>
       </c>
     </row>
   </sheetData>
@@ -3331,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2">
@@ -14015,10 +14026,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
@@ -23930,6 +23941,15 @@
       </c>
       <c r="C902" t="n">
         <v>2.88</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B903"/>
+      <c r="C903" t="n">
+        <v>2.69</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14009,6 +14009,14 @@
         <v>2.2938623682579</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>1.77914110429449</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -23947,7 +23955,9 @@
       <c r="A903" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="B903"/>
+      <c r="B903" t="n">
+        <v>0.288582739831996</v>
+      </c>
       <c r="C903" t="n">
         <v>2.69</v>
       </c>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -23962,6 +23962,15 @@
         <v>2.69</v>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B904"/>
+      <c r="C904" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14017,6 +14017,14 @@
         <v>1.77914110429449</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>2.38532110091743</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -23966,7 +23974,9 @@
       <c r="A904" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B904"/>
+      <c r="B904" t="n">
+        <v>0.537550535227043</v>
+      </c>
       <c r="C904" t="n">
         <v>3.07</v>
       </c>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>11.0762267516624</v>
+        <v>11.0762267516623</v>
       </c>
     </row>
     <row r="6">
@@ -1290,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21716544719759</v>
+        <v>3.21716544719757</v>
       </c>
     </row>
     <row r="7">
@@ -1386,7 +1386,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>3.71274680756832</v>
+        <v>3.7127468075683</v>
       </c>
     </row>
     <row r="19">
@@ -1394,7 +1394,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>5.70026341273309</v>
+        <v>5.70026341273311</v>
       </c>
     </row>
     <row r="20">
@@ -1450,7 +1450,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>8.59733479233691</v>
+        <v>8.59733479233689</v>
       </c>
     </row>
     <row r="27">
@@ -1458,7 +1458,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="n">
-        <v>1.26693581729738</v>
+        <v>1.26693581729735</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="n">
-        <v>0.033321503910333</v>
+        <v>0.0333215039103552</v>
       </c>
     </row>
     <row r="39">
@@ -1554,7 +1554,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="n">
-        <v>4.20437570606003</v>
+        <v>4.20437570606005</v>
       </c>
     </row>
     <row r="40">
@@ -1570,7 +1570,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="n">
-        <v>-2.04188428529272</v>
+        <v>-2.04188428529271</v>
       </c>
     </row>
     <row r="42">
@@ -1626,7 +1626,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="n">
-        <v>9.73182093181713</v>
+        <v>9.7318209318171</v>
       </c>
     </row>
     <row r="49">
@@ -1650,7 +1650,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="n">
-        <v>1.87285559720214</v>
+        <v>1.87285559720212</v>
       </c>
     </row>
     <row r="52">
@@ -1658,7 +1658,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="n">
-        <v>7.5844378205006</v>
+        <v>7.58443782050062</v>
       </c>
     </row>
     <row r="53">
@@ -1666,7 +1666,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="n">
-        <v>3.3518567606323</v>
+        <v>3.35185676063232</v>
       </c>
     </row>
     <row r="54">
@@ -1722,7 +1722,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="n">
-        <v>4.70961549504267</v>
+        <v>4.7096154950427</v>
       </c>
     </row>
     <row r="61">
@@ -1738,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="n">
-        <v>8.90899211220209</v>
+        <v>8.90899211220206</v>
       </c>
     </row>
     <row r="63">
@@ -1778,7 +1778,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="n">
-        <v>2.3720052253458</v>
+        <v>2.37200522534582</v>
       </c>
     </row>
     <row r="68">
@@ -1802,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="n">
-        <v>2.75050596656428</v>
+        <v>2.7505059665643</v>
       </c>
     </row>
     <row r="71">
@@ -1818,7 +1818,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="n">
-        <v>3.84696278939263</v>
+        <v>3.84696278939261</v>
       </c>
     </row>
     <row r="73">
@@ -1842,7 +1842,7 @@
         <v>75</v>
       </c>
       <c r="B75" t="n">
-        <v>2.96468766570013</v>
+        <v>2.96468766570011</v>
       </c>
     </row>
     <row r="76">
@@ -1874,7 +1874,7 @@
         <v>79</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.331950107110968</v>
+        <v>-0.331950107110979</v>
       </c>
     </row>
     <row r="80">
@@ -1954,7 +1954,7 @@
         <v>89</v>
       </c>
       <c r="B89" t="n">
-        <v>6.69907106451606</v>
+        <v>6.69907106451604</v>
       </c>
     </row>
     <row r="90">
@@ -1970,7 +1970,7 @@
         <v>91</v>
       </c>
       <c r="B91" t="n">
-        <v>4.57005411395808</v>
+        <v>4.57005411395806</v>
       </c>
     </row>
     <row r="92">
@@ -2010,7 +2010,7 @@
         <v>96</v>
       </c>
       <c r="B96" t="n">
-        <v>6.39040155294808</v>
+        <v>6.39040155294806</v>
       </c>
     </row>
     <row r="97">
@@ -2026,7 +2026,7 @@
         <v>98</v>
       </c>
       <c r="B98" t="n">
-        <v>1.29281489077719</v>
+        <v>1.29281489077722</v>
       </c>
     </row>
     <row r="99">
@@ -2042,7 +2042,7 @@
         <v>100</v>
       </c>
       <c r="B100" t="n">
-        <v>6.2392879351316</v>
+        <v>6.23928793513162</v>
       </c>
     </row>
     <row r="101">
@@ -2066,7 +2066,7 @@
         <v>103</v>
       </c>
       <c r="B103" t="n">
-        <v>0.503892947108686</v>
+        <v>0.503892947108664</v>
       </c>
     </row>
     <row r="104">
@@ -2114,7 +2114,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="n">
-        <v>5.95657317027753</v>
+        <v>5.95657317027756</v>
       </c>
     </row>
     <row r="110">
@@ -2154,7 +2154,7 @@
         <v>114</v>
       </c>
       <c r="B114" t="n">
-        <v>1.56510031417771</v>
+        <v>1.56510031417769</v>
       </c>
     </row>
     <row r="115">
@@ -2202,7 +2202,7 @@
         <v>120</v>
       </c>
       <c r="B120" t="n">
-        <v>-3.51432433036452</v>
+        <v>-3.51432433036453</v>
       </c>
     </row>
     <row r="121">
@@ -2210,7 +2210,7 @@
         <v>121</v>
       </c>
       <c r="B121" t="n">
-        <v>-5.63145982131693</v>
+        <v>-5.63145982131692</v>
       </c>
     </row>
     <row r="122">
@@ -2226,7 +2226,7 @@
         <v>123</v>
       </c>
       <c r="B123" t="n">
-        <v>0.53156216770216</v>
+        <v>0.531562167702138</v>
       </c>
     </row>
     <row r="124">
@@ -2250,7 +2250,7 @@
         <v>126</v>
       </c>
       <c r="B126" t="n">
-        <v>0.4566381198297</v>
+        <v>0.456638119829678</v>
       </c>
     </row>
     <row r="127">
@@ -2258,7 +2258,7 @@
         <v>127</v>
       </c>
       <c r="B127" t="n">
-        <v>2.18429723140845</v>
+        <v>2.18429723140843</v>
       </c>
     </row>
     <row r="128">
@@ -2274,7 +2274,7 @@
         <v>129</v>
       </c>
       <c r="B129" t="n">
-        <v>2.56397253570295</v>
+        <v>2.56397253570297</v>
       </c>
     </row>
     <row r="130">
@@ -2298,7 +2298,7 @@
         <v>132</v>
       </c>
       <c r="B132" t="n">
-        <v>1.72198017966116</v>
+        <v>1.72198017966119</v>
       </c>
     </row>
     <row r="133">
@@ -2306,7 +2306,7 @@
         <v>133</v>
       </c>
       <c r="B133" t="n">
-        <v>6.02964232282088</v>
+        <v>6.02964232282091</v>
       </c>
     </row>
     <row r="134">
@@ -2330,7 +2330,7 @@
         <v>136</v>
       </c>
       <c r="B136" t="n">
-        <v>2.93750438162366</v>
+        <v>2.93750438162368</v>
       </c>
     </row>
     <row r="137">
@@ -2354,7 +2354,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="n">
-        <v>0.529700089635199</v>
+        <v>0.529700089635177</v>
       </c>
     </row>
     <row r="140">
@@ -2378,7 +2378,7 @@
         <v>142</v>
       </c>
       <c r="B142" t="n">
-        <v>2.87822738230961</v>
+        <v>2.87822738230958</v>
       </c>
     </row>
     <row r="143">
@@ -2394,7 +2394,7 @@
         <v>144</v>
       </c>
       <c r="B144" t="n">
-        <v>3.20702698653901</v>
+        <v>3.20702698653903</v>
       </c>
     </row>
     <row r="145">
@@ -2402,7 +2402,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="n">
-        <v>5.46833467282353</v>
+        <v>5.4683346728235</v>
       </c>
     </row>
     <row r="146">
@@ -2426,7 +2426,7 @@
         <v>148</v>
       </c>
       <c r="B148" t="n">
-        <v>3.92196784230516</v>
+        <v>3.92196784230514</v>
       </c>
     </row>
     <row r="149">
@@ -2442,7 +2442,7 @@
         <v>150</v>
       </c>
       <c r="B150" t="n">
-        <v>0.211984764384443</v>
+        <v>0.211984764384465</v>
       </c>
     </row>
     <row r="151">
@@ -2474,7 +2474,7 @@
         <v>154</v>
       </c>
       <c r="B154" t="n">
-        <v>3.34006772083091</v>
+        <v>3.34006772083089</v>
       </c>
     </row>
     <row r="155">
@@ -2482,7 +2482,7 @@
         <v>155</v>
       </c>
       <c r="B155" t="n">
-        <v>6.41874079173079</v>
+        <v>6.41874079173077</v>
       </c>
     </row>
     <row r="156">
@@ -2554,7 +2554,7 @@
         <v>164</v>
       </c>
       <c r="B164" t="n">
-        <v>2.42067819855796</v>
+        <v>2.42067819855794</v>
       </c>
     </row>
     <row r="165">
@@ -2562,7 +2562,7 @@
         <v>165</v>
       </c>
       <c r="B165" t="n">
-        <v>5.97828399453673</v>
+        <v>5.97828399453675</v>
       </c>
     </row>
     <row r="166">
@@ -2586,7 +2586,7 @@
         <v>168</v>
       </c>
       <c r="B168" t="n">
-        <v>2.21512844173293</v>
+        <v>2.21512844173291</v>
       </c>
     </row>
     <row r="169">
@@ -2610,7 +2610,7 @@
         <v>171</v>
       </c>
       <c r="B171" t="n">
-        <v>1.50386111871783</v>
+        <v>1.50386111871785</v>
       </c>
     </row>
     <row r="172">
@@ -2650,7 +2650,7 @@
         <v>176</v>
       </c>
       <c r="B176" t="n">
-        <v>2.91826349240285</v>
+        <v>2.91826349240283</v>
       </c>
     </row>
     <row r="177">
@@ -2674,7 +2674,7 @@
         <v>179</v>
       </c>
       <c r="B179" t="n">
-        <v>4.93639310090215</v>
+        <v>4.93639310090213</v>
       </c>
     </row>
     <row r="180">
@@ -2698,7 +2698,7 @@
         <v>182</v>
       </c>
       <c r="B182" t="n">
-        <v>0.200177387764677</v>
+        <v>0.200177387764655</v>
       </c>
     </row>
     <row r="183">
@@ -2706,7 +2706,7 @@
         <v>183</v>
       </c>
       <c r="B183" t="n">
-        <v>1.13075224402648</v>
+        <v>1.13075224402646</v>
       </c>
     </row>
     <row r="184">
@@ -2714,7 +2714,7 @@
         <v>184</v>
       </c>
       <c r="B184" t="n">
-        <v>1.60246237088593</v>
+        <v>1.60246237088595</v>
       </c>
     </row>
     <row r="185">
@@ -2730,7 +2730,7 @@
         <v>186</v>
       </c>
       <c r="B186" t="n">
-        <v>3.91921021991077</v>
+        <v>3.91921021991075</v>
       </c>
     </row>
     <row r="187">
@@ -2738,7 +2738,7 @@
         <v>187</v>
       </c>
       <c r="B187" t="n">
-        <v>1.50716840650429</v>
+        <v>1.50716840650427</v>
       </c>
     </row>
     <row r="188">
@@ -2754,7 +2754,7 @@
         <v>189</v>
       </c>
       <c r="B189" t="n">
-        <v>0.300485955374752</v>
+        <v>0.300485955374774</v>
       </c>
     </row>
     <row r="190">
@@ -2770,7 +2770,7 @@
         <v>191</v>
       </c>
       <c r="B191" t="n">
-        <v>3.32769587375965</v>
+        <v>3.32769587375963</v>
       </c>
     </row>
     <row r="192">
@@ -2802,7 +2802,7 @@
         <v>195</v>
       </c>
       <c r="B195" t="n">
-        <v>1.80099930475093</v>
+        <v>1.80099930475091</v>
       </c>
     </row>
     <row r="196">
@@ -2810,7 +2810,7 @@
         <v>196</v>
       </c>
       <c r="B196" t="n">
-        <v>4.72922571233296</v>
+        <v>4.72922571233294</v>
       </c>
     </row>
     <row r="197">
@@ -2818,7 +2818,7 @@
         <v>197</v>
       </c>
       <c r="B197" t="n">
-        <v>4.93491458854942</v>
+        <v>4.93491458854944</v>
       </c>
     </row>
     <row r="198">
@@ -2842,7 +2842,7 @@
         <v>200</v>
       </c>
       <c r="B200" t="n">
-        <v>4.56327979056319</v>
+        <v>4.56327979056321</v>
       </c>
     </row>
     <row r="201">
@@ -2866,7 +2866,7 @@
         <v>203</v>
       </c>
       <c r="B203" t="n">
-        <v>5.5863519305944</v>
+        <v>5.58635193059442</v>
       </c>
     </row>
     <row r="204">
@@ -2898,7 +2898,7 @@
         <v>207</v>
       </c>
       <c r="B207" t="n">
-        <v>0.548542657841011</v>
+        <v>0.548542657841034</v>
       </c>
     </row>
     <row r="208">
@@ -2906,7 +2906,7 @@
         <v>208</v>
       </c>
       <c r="B208" t="n">
-        <v>0.825740775376982</v>
+        <v>0.82574077537696</v>
       </c>
     </row>
     <row r="209">
@@ -2922,7 +2922,7 @@
         <v>210</v>
       </c>
       <c r="B210" t="n">
-        <v>2.32352993374909</v>
+        <v>2.32352993374907</v>
       </c>
     </row>
     <row r="211">
@@ -2930,7 +2930,7 @@
         <v>211</v>
       </c>
       <c r="B211" t="n">
-        <v>3.33004257497442</v>
+        <v>3.3300425749744</v>
       </c>
     </row>
     <row r="212">
@@ -2962,7 +2962,7 @@
         <v>215</v>
       </c>
       <c r="B215" t="n">
-        <v>3.88978244833267</v>
+        <v>3.88978244833265</v>
       </c>
     </row>
     <row r="216">
@@ -2994,7 +2994,7 @@
         <v>219</v>
       </c>
       <c r="B219" t="n">
-        <v>1.44010249116646</v>
+        <v>1.44010249116648</v>
       </c>
     </row>
     <row r="220">
@@ -3002,7 +3002,7 @@
         <v>220</v>
       </c>
       <c r="B220" t="n">
-        <v>0.265351951557569</v>
+        <v>0.265351951557591</v>
       </c>
     </row>
     <row r="221">
@@ -3018,7 +3018,7 @@
         <v>222</v>
       </c>
       <c r="B222" t="n">
-        <v>-1.97769685012743</v>
+        <v>-1.97769685012744</v>
       </c>
     </row>
     <row r="223">
@@ -3026,7 +3026,7 @@
         <v>223</v>
       </c>
       <c r="B223" t="n">
-        <v>4.21620319070606</v>
+        <v>4.21620319070608</v>
       </c>
     </row>
     <row r="224">
@@ -3034,7 +3034,7 @@
         <v>224</v>
       </c>
       <c r="B224" t="n">
-        <v>2.26304459146593</v>
+        <v>2.26304459146596</v>
       </c>
     </row>
     <row r="225">
@@ -3042,7 +3042,7 @@
         <v>225</v>
       </c>
       <c r="B225" t="n">
-        <v>5.12860841207206</v>
+        <v>5.12860841207208</v>
       </c>
     </row>
     <row r="226">
@@ -3058,7 +3058,7 @@
         <v>227</v>
       </c>
       <c r="B227" t="n">
-        <v>0.125667740338975</v>
+        <v>0.125667740338997</v>
       </c>
     </row>
     <row r="228">
@@ -3098,7 +3098,7 @@
         <v>232</v>
       </c>
       <c r="B232" t="n">
-        <v>0.945609372131373</v>
+        <v>0.945609372131395</v>
       </c>
     </row>
     <row r="233">
@@ -3114,7 +3114,7 @@
         <v>234</v>
       </c>
       <c r="B234" t="n">
-        <v>4.45149614738636</v>
+        <v>4.45149614738638</v>
       </c>
     </row>
     <row r="235">
@@ -3178,7 +3178,7 @@
         <v>242</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.467958376300814</v>
+        <v>-0.467958376300825</v>
       </c>
     </row>
     <row r="243">
@@ -3194,7 +3194,7 @@
         <v>244</v>
       </c>
       <c r="B244" t="n">
-        <v>7.35624562757611</v>
+        <v>7.35624562757613</v>
       </c>
     </row>
     <row r="245">
@@ -3218,7 +3218,7 @@
         <v>247</v>
       </c>
       <c r="B247" t="n">
-        <v>3.27452200666154</v>
+        <v>3.27452200666156</v>
       </c>
     </row>
     <row r="248">
@@ -3234,7 +3234,7 @@
         <v>249</v>
       </c>
       <c r="B249" t="n">
-        <v>4.27765146518027</v>
+        <v>4.27765146518029</v>
       </c>
     </row>
     <row r="250">
@@ -3274,7 +3274,7 @@
         <v>254</v>
       </c>
       <c r="B254" t="n">
-        <v>3.30413514808308</v>
+        <v>3.30413514808305</v>
       </c>
     </row>
     <row r="255">
@@ -3290,7 +3290,7 @@
         <v>256</v>
       </c>
       <c r="B256" t="n">
-        <v>2.8353824208952</v>
+        <v>2.83538242089523</v>
       </c>
     </row>
     <row r="257">
@@ -3306,7 +3306,7 @@
         <v>258</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.937137943003352</v>
+        <v>-0.937137943003341</v>
       </c>
     </row>
     <row r="259">
@@ -3314,7 +3314,7 @@
         <v>259</v>
       </c>
       <c r="B259" t="n">
-        <v>2.38566269456462</v>
+        <v>2.38566269456459</v>
       </c>
     </row>
     <row r="260">
@@ -23981,6 +23981,15 @@
         <v>3.07</v>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B905"/>
+      <c r="C905" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -797,6 +797,9 @@
   </si>
   <si>
     <t xml:space="preserve">Oct 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan 2026</t>
   </si>
   <si>
     <t xml:space="preserve">inflation</t>
@@ -1282,7 +1285,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>11.0762267516623</v>
+        <v>11.0762267516624</v>
       </c>
     </row>
     <row r="6">
@@ -1290,7 +1293,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21716544719757</v>
+        <v>3.21716544719759</v>
       </c>
     </row>
     <row r="7">
@@ -1386,7 +1389,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>3.7127468075683</v>
+        <v>3.71274680756832</v>
       </c>
     </row>
     <row r="19">
@@ -1394,7 +1397,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>5.70026341273311</v>
+        <v>5.70026341273309</v>
       </c>
     </row>
     <row r="20">
@@ -1450,7 +1453,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>8.59733479233689</v>
+        <v>8.59733479233691</v>
       </c>
     </row>
     <row r="27">
@@ -1458,7 +1461,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="n">
-        <v>1.26693581729735</v>
+        <v>1.26693581729738</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1549,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0333215039103552</v>
+        <v>0.033321503910333</v>
       </c>
     </row>
     <row r="39">
@@ -1554,7 +1557,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="n">
-        <v>4.20437570606005</v>
+        <v>4.20437570606003</v>
       </c>
     </row>
     <row r="40">
@@ -1570,7 +1573,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="n">
-        <v>-2.04188428529271</v>
+        <v>-2.04188428529272</v>
       </c>
     </row>
     <row r="42">
@@ -1626,7 +1629,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="n">
-        <v>9.7318209318171</v>
+        <v>9.73182093181713</v>
       </c>
     </row>
     <row r="49">
@@ -1650,7 +1653,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="n">
-        <v>1.87285559720212</v>
+        <v>1.87285559720214</v>
       </c>
     </row>
     <row r="52">
@@ -1658,7 +1661,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="n">
-        <v>7.58443782050062</v>
+        <v>7.5844378205006</v>
       </c>
     </row>
     <row r="53">
@@ -1666,7 +1669,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="n">
-        <v>3.35185676063232</v>
+        <v>3.3518567606323</v>
       </c>
     </row>
     <row r="54">
@@ -1722,7 +1725,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="n">
-        <v>4.7096154950427</v>
+        <v>4.70961549504267</v>
       </c>
     </row>
     <row r="61">
@@ -1738,7 +1741,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="n">
-        <v>8.90899211220206</v>
+        <v>8.90899211220209</v>
       </c>
     </row>
     <row r="63">
@@ -1778,7 +1781,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="n">
-        <v>2.37200522534582</v>
+        <v>2.3720052253458</v>
       </c>
     </row>
     <row r="68">
@@ -1802,7 +1805,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="n">
-        <v>2.7505059665643</v>
+        <v>2.75050596656428</v>
       </c>
     </row>
     <row r="71">
@@ -1818,7 +1821,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="n">
-        <v>3.84696278939261</v>
+        <v>3.84696278939263</v>
       </c>
     </row>
     <row r="73">
@@ -1842,7 +1845,7 @@
         <v>75</v>
       </c>
       <c r="B75" t="n">
-        <v>2.96468766570011</v>
+        <v>2.96468766570013</v>
       </c>
     </row>
     <row r="76">
@@ -1874,7 +1877,7 @@
         <v>79</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.331950107110979</v>
+        <v>-0.331950107110968</v>
       </c>
     </row>
     <row r="80">
@@ -1954,7 +1957,7 @@
         <v>89</v>
       </c>
       <c r="B89" t="n">
-        <v>6.69907106451604</v>
+        <v>6.69907106451606</v>
       </c>
     </row>
     <row r="90">
@@ -1970,7 +1973,7 @@
         <v>91</v>
       </c>
       <c r="B91" t="n">
-        <v>4.57005411395806</v>
+        <v>4.57005411395808</v>
       </c>
     </row>
     <row r="92">
@@ -2010,7 +2013,7 @@
         <v>96</v>
       </c>
       <c r="B96" t="n">
-        <v>6.39040155294806</v>
+        <v>6.39040155294808</v>
       </c>
     </row>
     <row r="97">
@@ -2026,7 +2029,7 @@
         <v>98</v>
       </c>
       <c r="B98" t="n">
-        <v>1.29281489077722</v>
+        <v>1.29281489077719</v>
       </c>
     </row>
     <row r="99">
@@ -2042,7 +2045,7 @@
         <v>100</v>
       </c>
       <c r="B100" t="n">
-        <v>6.23928793513162</v>
+        <v>6.2392879351316</v>
       </c>
     </row>
     <row r="101">
@@ -2066,7 +2069,7 @@
         <v>103</v>
       </c>
       <c r="B103" t="n">
-        <v>0.503892947108664</v>
+        <v>0.503892947108686</v>
       </c>
     </row>
     <row r="104">
@@ -2114,7 +2117,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="n">
-        <v>5.95657317027756</v>
+        <v>5.95657317027753</v>
       </c>
     </row>
     <row r="110">
@@ -2154,7 +2157,7 @@
         <v>114</v>
       </c>
       <c r="B114" t="n">
-        <v>1.56510031417769</v>
+        <v>1.56510031417771</v>
       </c>
     </row>
     <row r="115">
@@ -2202,7 +2205,7 @@
         <v>120</v>
       </c>
       <c r="B120" t="n">
-        <v>-3.51432433036453</v>
+        <v>-3.51432433036452</v>
       </c>
     </row>
     <row r="121">
@@ -2210,7 +2213,7 @@
         <v>121</v>
       </c>
       <c r="B121" t="n">
-        <v>-5.63145982131692</v>
+        <v>-5.63145982131693</v>
       </c>
     </row>
     <row r="122">
@@ -2226,7 +2229,7 @@
         <v>123</v>
       </c>
       <c r="B123" t="n">
-        <v>0.531562167702138</v>
+        <v>0.53156216770216</v>
       </c>
     </row>
     <row r="124">
@@ -2250,7 +2253,7 @@
         <v>126</v>
       </c>
       <c r="B126" t="n">
-        <v>0.456638119829678</v>
+        <v>0.4566381198297</v>
       </c>
     </row>
     <row r="127">
@@ -2258,7 +2261,7 @@
         <v>127</v>
       </c>
       <c r="B127" t="n">
-        <v>2.18429723140843</v>
+        <v>2.18429723140845</v>
       </c>
     </row>
     <row r="128">
@@ -2274,7 +2277,7 @@
         <v>129</v>
       </c>
       <c r="B129" t="n">
-        <v>2.56397253570297</v>
+        <v>2.56397253570295</v>
       </c>
     </row>
     <row r="130">
@@ -2298,7 +2301,7 @@
         <v>132</v>
       </c>
       <c r="B132" t="n">
-        <v>1.72198017966119</v>
+        <v>1.72198017966116</v>
       </c>
     </row>
     <row r="133">
@@ -2306,7 +2309,7 @@
         <v>133</v>
       </c>
       <c r="B133" t="n">
-        <v>6.02964232282091</v>
+        <v>6.02964232282088</v>
       </c>
     </row>
     <row r="134">
@@ -2330,7 +2333,7 @@
         <v>136</v>
       </c>
       <c r="B136" t="n">
-        <v>2.93750438162368</v>
+        <v>2.93750438162366</v>
       </c>
     </row>
     <row r="137">
@@ -2354,7 +2357,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="n">
-        <v>0.529700089635177</v>
+        <v>0.529700089635199</v>
       </c>
     </row>
     <row r="140">
@@ -2378,7 +2381,7 @@
         <v>142</v>
       </c>
       <c r="B142" t="n">
-        <v>2.87822738230958</v>
+        <v>2.87822738230961</v>
       </c>
     </row>
     <row r="143">
@@ -2394,7 +2397,7 @@
         <v>144</v>
       </c>
       <c r="B144" t="n">
-        <v>3.20702698653903</v>
+        <v>3.20702698653901</v>
       </c>
     </row>
     <row r="145">
@@ -2402,7 +2405,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="n">
-        <v>5.4683346728235</v>
+        <v>5.46833467282353</v>
       </c>
     </row>
     <row r="146">
@@ -2426,7 +2429,7 @@
         <v>148</v>
       </c>
       <c r="B148" t="n">
-        <v>3.92196784230514</v>
+        <v>3.92196784230516</v>
       </c>
     </row>
     <row r="149">
@@ -2442,7 +2445,7 @@
         <v>150</v>
       </c>
       <c r="B150" t="n">
-        <v>0.211984764384465</v>
+        <v>0.211984764384443</v>
       </c>
     </row>
     <row r="151">
@@ -2474,7 +2477,7 @@
         <v>154</v>
       </c>
       <c r="B154" t="n">
-        <v>3.34006772083089</v>
+        <v>3.34006772083091</v>
       </c>
     </row>
     <row r="155">
@@ -2482,7 +2485,7 @@
         <v>155</v>
       </c>
       <c r="B155" t="n">
-        <v>6.41874079173077</v>
+        <v>6.41874079173079</v>
       </c>
     </row>
     <row r="156">
@@ -2554,7 +2557,7 @@
         <v>164</v>
       </c>
       <c r="B164" t="n">
-        <v>2.42067819855794</v>
+        <v>2.42067819855796</v>
       </c>
     </row>
     <row r="165">
@@ -2562,7 +2565,7 @@
         <v>165</v>
       </c>
       <c r="B165" t="n">
-        <v>5.97828399453675</v>
+        <v>5.97828399453673</v>
       </c>
     </row>
     <row r="166">
@@ -2586,7 +2589,7 @@
         <v>168</v>
       </c>
       <c r="B168" t="n">
-        <v>2.21512844173291</v>
+        <v>2.21512844173293</v>
       </c>
     </row>
     <row r="169">
@@ -2610,7 +2613,7 @@
         <v>171</v>
       </c>
       <c r="B171" t="n">
-        <v>1.50386111871785</v>
+        <v>1.50386111871783</v>
       </c>
     </row>
     <row r="172">
@@ -2650,7 +2653,7 @@
         <v>176</v>
       </c>
       <c r="B176" t="n">
-        <v>2.91826349240283</v>
+        <v>2.91826349240285</v>
       </c>
     </row>
     <row r="177">
@@ -2674,7 +2677,7 @@
         <v>179</v>
       </c>
       <c r="B179" t="n">
-        <v>4.93639310090213</v>
+        <v>4.93639310090215</v>
       </c>
     </row>
     <row r="180">
@@ -2698,7 +2701,7 @@
         <v>182</v>
       </c>
       <c r="B182" t="n">
-        <v>0.200177387764655</v>
+        <v>0.200177387764677</v>
       </c>
     </row>
     <row r="183">
@@ -2706,7 +2709,7 @@
         <v>183</v>
       </c>
       <c r="B183" t="n">
-        <v>1.13075224402646</v>
+        <v>1.13075224402648</v>
       </c>
     </row>
     <row r="184">
@@ -2714,7 +2717,7 @@
         <v>184</v>
       </c>
       <c r="B184" t="n">
-        <v>1.60246237088595</v>
+        <v>1.60246237088593</v>
       </c>
     </row>
     <row r="185">
@@ -2730,7 +2733,7 @@
         <v>186</v>
       </c>
       <c r="B186" t="n">
-        <v>3.91921021991075</v>
+        <v>3.91921021991077</v>
       </c>
     </row>
     <row r="187">
@@ -2738,7 +2741,7 @@
         <v>187</v>
       </c>
       <c r="B187" t="n">
-        <v>1.50716840650427</v>
+        <v>1.50716840650429</v>
       </c>
     </row>
     <row r="188">
@@ -2754,7 +2757,7 @@
         <v>189</v>
       </c>
       <c r="B189" t="n">
-        <v>0.300485955374774</v>
+        <v>0.300485955374752</v>
       </c>
     </row>
     <row r="190">
@@ -2770,7 +2773,7 @@
         <v>191</v>
       </c>
       <c r="B191" t="n">
-        <v>3.32769587375963</v>
+        <v>3.32769587375965</v>
       </c>
     </row>
     <row r="192">
@@ -2802,7 +2805,7 @@
         <v>195</v>
       </c>
       <c r="B195" t="n">
-        <v>1.80099930475091</v>
+        <v>1.80099930475093</v>
       </c>
     </row>
     <row r="196">
@@ -2810,7 +2813,7 @@
         <v>196</v>
       </c>
       <c r="B196" t="n">
-        <v>4.72922571233294</v>
+        <v>4.72922571233296</v>
       </c>
     </row>
     <row r="197">
@@ -2818,7 +2821,7 @@
         <v>197</v>
       </c>
       <c r="B197" t="n">
-        <v>4.93491458854944</v>
+        <v>4.93491458854942</v>
       </c>
     </row>
     <row r="198">
@@ -2842,7 +2845,7 @@
         <v>200</v>
       </c>
       <c r="B200" t="n">
-        <v>4.56327979056321</v>
+        <v>4.56327979056319</v>
       </c>
     </row>
     <row r="201">
@@ -2866,7 +2869,7 @@
         <v>203</v>
       </c>
       <c r="B203" t="n">
-        <v>5.58635193059442</v>
+        <v>5.5863519305944</v>
       </c>
     </row>
     <row r="204">
@@ -2898,7 +2901,7 @@
         <v>207</v>
       </c>
       <c r="B207" t="n">
-        <v>0.548542657841034</v>
+        <v>0.548542657841011</v>
       </c>
     </row>
     <row r="208">
@@ -2906,7 +2909,7 @@
         <v>208</v>
       </c>
       <c r="B208" t="n">
-        <v>0.82574077537696</v>
+        <v>0.825740775376982</v>
       </c>
     </row>
     <row r="209">
@@ -2922,7 +2925,7 @@
         <v>210</v>
       </c>
       <c r="B210" t="n">
-        <v>2.32352993374907</v>
+        <v>2.32352993374909</v>
       </c>
     </row>
     <row r="211">
@@ -2930,7 +2933,7 @@
         <v>211</v>
       </c>
       <c r="B211" t="n">
-        <v>3.3300425749744</v>
+        <v>3.33004257497442</v>
       </c>
     </row>
     <row r="212">
@@ -2962,7 +2965,7 @@
         <v>215</v>
       </c>
       <c r="B215" t="n">
-        <v>3.88978244833265</v>
+        <v>3.88978244833267</v>
       </c>
     </row>
     <row r="216">
@@ -2994,7 +2997,7 @@
         <v>219</v>
       </c>
       <c r="B219" t="n">
-        <v>1.44010249116648</v>
+        <v>1.44010249116646</v>
       </c>
     </row>
     <row r="220">
@@ -3002,7 +3005,7 @@
         <v>220</v>
       </c>
       <c r="B220" t="n">
-        <v>0.265351951557591</v>
+        <v>0.265351951557569</v>
       </c>
     </row>
     <row r="221">
@@ -3018,7 +3021,7 @@
         <v>222</v>
       </c>
       <c r="B222" t="n">
-        <v>-1.97769685012744</v>
+        <v>-1.97769685012743</v>
       </c>
     </row>
     <row r="223">
@@ -3026,7 +3029,7 @@
         <v>223</v>
       </c>
       <c r="B223" t="n">
-        <v>4.21620319070608</v>
+        <v>4.21620319070606</v>
       </c>
     </row>
     <row r="224">
@@ -3034,7 +3037,7 @@
         <v>224</v>
       </c>
       <c r="B224" t="n">
-        <v>2.26304459146596</v>
+        <v>2.26304459146593</v>
       </c>
     </row>
     <row r="225">
@@ -3042,7 +3045,7 @@
         <v>225</v>
       </c>
       <c r="B225" t="n">
-        <v>5.12860841207208</v>
+        <v>5.12860841207206</v>
       </c>
     </row>
     <row r="226">
@@ -3058,7 +3061,7 @@
         <v>227</v>
       </c>
       <c r="B227" t="n">
-        <v>0.125667740338997</v>
+        <v>0.125667740338975</v>
       </c>
     </row>
     <row r="228">
@@ -3098,7 +3101,7 @@
         <v>232</v>
       </c>
       <c r="B232" t="n">
-        <v>0.945609372131395</v>
+        <v>0.945609372131373</v>
       </c>
     </row>
     <row r="233">
@@ -3114,7 +3117,7 @@
         <v>234</v>
       </c>
       <c r="B234" t="n">
-        <v>4.45149614738638</v>
+        <v>4.45149614738636</v>
       </c>
     </row>
     <row r="235">
@@ -3178,7 +3181,7 @@
         <v>242</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.467958376300825</v>
+        <v>-0.467958376300814</v>
       </c>
     </row>
     <row r="243">
@@ -3194,7 +3197,7 @@
         <v>244</v>
       </c>
       <c r="B244" t="n">
-        <v>7.35624562757613</v>
+        <v>7.35624562757611</v>
       </c>
     </row>
     <row r="245">
@@ -3218,7 +3221,7 @@
         <v>247</v>
       </c>
       <c r="B247" t="n">
-        <v>3.27452200666156</v>
+        <v>3.27452200666154</v>
       </c>
     </row>
     <row r="248">
@@ -3234,7 +3237,7 @@
         <v>249</v>
       </c>
       <c r="B249" t="n">
-        <v>4.27765146518029</v>
+        <v>4.27765146518027</v>
       </c>
     </row>
     <row r="250">
@@ -3274,7 +3277,7 @@
         <v>254</v>
       </c>
       <c r="B254" t="n">
-        <v>3.30413514808305</v>
+        <v>3.30413514808308</v>
       </c>
     </row>
     <row r="255">
@@ -3290,7 +3293,7 @@
         <v>256</v>
       </c>
       <c r="B256" t="n">
-        <v>2.83538242089523</v>
+        <v>2.8353824208952</v>
       </c>
     </row>
     <row r="257">
@@ -3298,7 +3301,7 @@
         <v>257</v>
       </c>
       <c r="B257" t="n">
-        <v>2.08398976978965</v>
+        <v>2.89321069711812</v>
       </c>
     </row>
     <row r="258">
@@ -3306,7 +3309,7 @@
         <v>258</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.937137943003341</v>
+        <v>-0.965772312724966</v>
       </c>
     </row>
     <row r="259">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="B259" t="n">
-        <v>2.38566269456459</v>
+        <v>1.90108375057234</v>
       </c>
     </row>
     <row r="260">
@@ -3322,7 +3325,15 @@
         <v>260</v>
       </c>
       <c r="B260" t="n">
-        <v>-0.604381240998075</v>
+        <v>-0.982263100392011</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.142713715769993</v>
       </c>
     </row>
   </sheetData>
@@ -3342,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2">
@@ -14023,6 +14034,14 @@
       </c>
       <c r="B1336" t="n">
         <v>2.38532110091743</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>2.81517747858018</v>
       </c>
     </row>
   </sheetData>
@@ -14042,10 +14061,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2">
@@ -23985,9 +24004,20 @@
       <c r="A905" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="B905"/>
+      <c r="B905" t="n">
+        <v>0.786428662268388</v>
+      </c>
       <c r="C905" t="n">
         <v>3.2</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B906"/>
+      <c r="C906" t="n">
+        <v>3.07</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14044,6 +14044,14 @@
         <v>2.81517747858018</v>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1338" t="n">
+        <v>3.2258064516129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -24015,9 +24023,20 @@
       <c r="A906" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="B906"/>
+      <c r="B906" t="n">
+        <v>0.463376006661625</v>
+      </c>
       <c r="C906" t="n">
         <v>3.07</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B907"/>
+      <c r="C907" t="n">
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C02 Figures.xlsx
+++ b/Data/C02 Figures.xlsx
@@ -14052,6 +14052,14 @@
         <v>3.2258064516129</v>
       </c>
     </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B1339" t="n">
+        <v>2.79805352798053</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -24034,7 +24042,9 @@
       <c r="A907" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="B907"/>
+      <c r="B907" t="n">
+        <v>0.507998681938019</v>
+      </c>
       <c r="C907" t="n">
         <v>2.95</v>
       </c>
